--- a/output/table3_nitrate_deltas.xlsx
+++ b/output/table3_nitrate_deltas.xlsx
@@ -1,76 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kantn\Dropbox\Dokumenty\US_Boulder\GitHub\2023_kantnerova_et_al\output\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F42099-E631-47E7-AC00-FEC0EE749B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="dataset" sheetId="1" r:id="rId1"/>
+    <sheet name="dataset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>isotopocule_ratio</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
-    <t>reference_ratio</t>
-  </si>
-  <si>
-    <t>ratio_corrected_mean</t>
-  </si>
-  <si>
-    <t>delta_expected</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>delta_mean</t>
-  </si>
-  <si>
-    <t>delta_sdev</t>
-  </si>
-  <si>
-    <t>15N/M0</t>
-  </si>
-  <si>
-    <t>Air-N2</t>
-  </si>
-  <si>
-    <t>17O/M0</t>
-  </si>
-  <si>
-    <t>VSMOW</t>
-  </si>
-  <si>
-    <t>18O/M0</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t xml:space="preserve">isotopocule_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reference_ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratio_corrected_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delta_expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delta_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delta_sdev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15N/M0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air-N2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17O/M0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSMOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18O/M0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0000000"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -79,10 +70,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b/>
     </font>
     <font>
       <sz val="11"/>
@@ -110,27 +101,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -412,21 +392,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="1.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="1.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="11.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,85 +432,85 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4">
-        <v>3.676E-3</v>
-      </c>
-      <c r="D2" s="4">
-        <v>4.3452877054515598E-3</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="C2" s="3" t="n">
+        <v>0.003676</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.00434528770545156</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="5">
-        <v>182.06956078660599</v>
-      </c>
-      <c r="H2" s="5">
+      <c r="G2" s="3" t="n">
+        <v>182.069560786606</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>1.22838281793701</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4">
-        <v>1.14E-3</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.1538485507992099E-3</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="C3" s="3" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.00115384855079921</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3" t="n">
         <v>12.1478515782588</v>
       </c>
-      <c r="H3" s="5">
-        <v>2.3541611044764599</v>
+      <c r="H3" s="3" t="n">
+        <v>2.35416110447646</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4">
-        <v>6.0159999999999996E-3</v>
-      </c>
-      <c r="D4" s="4">
-        <v>6.1798331159733499E-3</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="C4" s="3" t="n">
+        <v>0.006016</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.00617983311597335</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="5">
-        <v>27.232898266847101</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G4" s="3" t="n">
+        <v>27.2328982668471</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1.44912547130403</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -540,6 +520,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>